--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.62281264696835</v>
+        <v>4.001207055132356</v>
       </c>
       <c r="D2" t="n">
-        <v>6.521337344896075</v>
+        <v>1.059717318545612</v>
       </c>
       <c r="E2" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F2" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.61275002592968</v>
+        <v>3.187071879213573</v>
       </c>
       <c r="D3" t="n">
-        <v>17.35812615852054</v>
+        <v>2.820695500759589</v>
       </c>
       <c r="E3" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F3" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.91681222585975</v>
+        <v>4.048981986702209</v>
       </c>
       <c r="D4" t="n">
-        <v>24.52189758335879</v>
+        <v>3.984808357295804</v>
       </c>
       <c r="E4" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F4" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.41215769586692</v>
+        <v>4.616975625578375</v>
       </c>
       <c r="D5" t="n">
-        <v>19.55613272789497</v>
+        <v>3.177871568282932</v>
       </c>
       <c r="E5" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F5" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.06020854639578</v>
+        <v>8.134783888789315</v>
       </c>
       <c r="D6" t="n">
-        <v>48.88713986255014</v>
+        <v>7.944160227664399</v>
       </c>
       <c r="E6" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F6" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.0938542745452</v>
+        <v>3.265251319613596</v>
       </c>
       <c r="D7" t="n">
-        <v>19.1907231156669</v>
+        <v>3.118492506295872</v>
       </c>
       <c r="E7" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F7" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.05638548778274</v>
+        <v>7.321662641764696</v>
       </c>
       <c r="D8" t="n">
-        <v>45.23930884307103</v>
+        <v>7.351387686999042</v>
       </c>
       <c r="E8" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F8" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.31671339148951</v>
+        <v>7.363965926117046</v>
       </c>
       <c r="D9" t="n">
-        <v>45.34326956538321</v>
+        <v>7.368281304374772</v>
       </c>
       <c r="E9" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F9" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.87559232293054</v>
+        <v>8.429783752476213</v>
       </c>
       <c r="D10" t="n">
-        <v>51.62640645283697</v>
+        <v>8.389291048586008</v>
       </c>
       <c r="E10" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F10" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.50930710252397</v>
+        <v>6.582762404160145</v>
       </c>
       <c r="D11" t="n">
-        <v>40.50098627316142</v>
+        <v>6.581410269388732</v>
       </c>
       <c r="E11" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F11" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.50862985399323</v>
+        <v>6.257652351273901</v>
       </c>
       <c r="D12" t="n">
-        <v>38.53430178096325</v>
+        <v>6.261824039406529</v>
       </c>
       <c r="E12" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F12" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.84798751808</v>
+        <v>5.012797971688001</v>
       </c>
       <c r="D13" t="n">
-        <v>31.54280430605271</v>
+        <v>5.125705699733566</v>
       </c>
       <c r="E13" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F13" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.35682472379564</v>
+        <v>8.182984017616791</v>
       </c>
       <c r="D14" t="n">
-        <v>50.14517755365248</v>
+        <v>8.148591352468529</v>
       </c>
       <c r="E14" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F14" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.39926067616972</v>
+        <v>3.314879859877579</v>
       </c>
       <c r="D15" t="n">
-        <v>21.09327656171433</v>
+        <v>3.427657441278579</v>
       </c>
       <c r="E15" t="n">
-        <v>11.77093566084346</v>
+        <v>1.912777044887062</v>
       </c>
       <c r="F15" t="n">
-        <v>14.18015773762657</v>
+        <v>2.304275632364318</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
